--- a/TestData.xlsx
+++ b/TestData.xlsx
@@ -370,7 +370,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>7798859042</v>
+        <v>77988590421</v>
       </c>
     </row>
   </sheetData>
